--- a/output/yearly_benthic_cover_iteration_91_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_91_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.05763538157779</v>
+        <v>45.00948193861696</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0670349738145</v>
+        <v>100.9350178684576</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.07805994741419</v>
+        <v>88.07379916237775</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9363173889808</v>
+        <v>45.95119632085406</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228854949413175</v>
+        <v>2.228832750091295</v>
       </c>
       <c r="E3" t="n">
-        <v>5.713541752399864</v>
+        <v>5.721741065249128</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429516498043918</v>
+        <v>0.7429442500304315</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97523013598439</v>
+        <v>33.9804532953767</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17577589100202</v>
+        <v>34.17543550139985</v>
       </c>
       <c r="I3" t="n">
-        <v>6.598257757532902</v>
+        <v>6.580990737540162</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643447811277449</v>
+        <v>4.643401562690197</v>
       </c>
       <c r="K3" t="n">
-        <v>11.92194005258581</v>
+        <v>11.92620083762225</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90491215332263</v>
+        <v>48.88638984663584</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7631695948892</v>
+        <v>106.7637870051121</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.27145679035866</v>
+        <v>87.19150791528384</v>
       </c>
       <c r="C4" t="n">
-        <v>42.77040001909252</v>
+        <v>42.70570660497867</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190566600012764</v>
+        <v>2.186519035570798</v>
       </c>
       <c r="E4" t="n">
-        <v>6.533745153243669</v>
+        <v>6.529062405696673</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445152587762941</v>
+        <v>0.7445051760198567</v>
       </c>
       <c r="G4" t="n">
-        <v>33.39158718391681</v>
+        <v>33.3353446841726</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24770190370953</v>
+        <v>34.24723809691341</v>
       </c>
       <c r="I4" t="n">
-        <v>5.510120323347745</v>
+        <v>5.495681166786398</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653220367351839</v>
+        <v>4.653157350124105</v>
       </c>
       <c r="K4" t="n">
-        <v>12.72854320964135</v>
+        <v>12.80849208471616</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31777183355688</v>
+        <v>44.30299601204018</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81671506229075</v>
+        <v>99.81719470173502</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.19217971895281</v>
+        <v>86.0601360792049</v>
       </c>
       <c r="C5" t="n">
-        <v>42.54643161389757</v>
+        <v>42.42734851632353</v>
       </c>
       <c r="D5" t="n">
-        <v>2.138227392833708</v>
+        <v>2.131472086819653</v>
       </c>
       <c r="E5" t="n">
-        <v>7.144290288534419</v>
+        <v>7.129334699671099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458397107682344</v>
+        <v>0.7458281636355483</v>
       </c>
       <c r="G5" t="n">
-        <v>32.59376200040203</v>
+        <v>32.49610707380695</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30862669533878</v>
+        <v>34.30809552723522</v>
       </c>
       <c r="I5" t="n">
-        <v>4.599935438774187</v>
+        <v>4.58787250531424</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661498192301465</v>
+        <v>4.661426022722178</v>
       </c>
       <c r="K5" t="n">
-        <v>13.80782028104718</v>
+        <v>13.9398639207951</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49268920718448</v>
+        <v>43.48012975269285</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84694110212922</v>
+        <v>99.84734218981149</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.79722093659066</v>
+        <v>84.69928954160409</v>
       </c>
       <c r="C6" t="n">
-        <v>41.8660405322282</v>
+        <v>41.77910000095942</v>
       </c>
       <c r="D6" t="n">
-        <v>2.070119321551239</v>
+        <v>2.065115217254673</v>
       </c>
       <c r="E6" t="n">
-        <v>7.556570235573147</v>
+        <v>7.545549366286759</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469652691477608</v>
+        <v>0.7469520484285483</v>
       </c>
       <c r="G6" t="n">
-        <v>31.55556640290515</v>
+        <v>31.48444008937852</v>
       </c>
       <c r="H6" t="n">
-        <v>34.360402380797</v>
+        <v>34.35979422771322</v>
       </c>
       <c r="I6" t="n">
-        <v>3.839064394442878</v>
+        <v>3.828988289863938</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668532932173505</v>
+        <v>4.668450302678428</v>
       </c>
       <c r="K6" t="n">
-        <v>15.20277906340933</v>
+        <v>15.30071045839592</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80340441995207</v>
+        <v>42.79274863771926</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87222401558961</v>
+        <v>99.8725590970746</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.14407965856857</v>
+        <v>83.12152468930702</v>
       </c>
       <c r="C7" t="n">
-        <v>40.80928333927227</v>
+        <v>40.79609579819922</v>
       </c>
       <c r="D7" t="n">
-        <v>1.98957226025799</v>
+        <v>1.988373510114499</v>
       </c>
       <c r="E7" t="n">
-        <v>7.796436919188559</v>
+        <v>7.797634638025388</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479245579148596</v>
+        <v>0.7479090592096175</v>
       </c>
       <c r="G7" t="n">
-        <v>30.32775884865587</v>
+        <v>30.31444741263893</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40452966408354</v>
+        <v>34.40381672364241</v>
       </c>
       <c r="I7" t="n">
-        <v>3.203328921499892</v>
+        <v>3.194911725616077</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674528486967873</v>
+        <v>4.67443162006011</v>
       </c>
       <c r="K7" t="n">
-        <v>16.85592034143142</v>
+        <v>16.87847531069296</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2281556416729</v>
+        <v>42.21906810527827</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8933593223766</v>
+        <v>99.89363921417045</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.01655662683243</v>
+        <v>87.99761080186809</v>
       </c>
       <c r="C8" t="n">
-        <v>43.12254517594524</v>
+        <v>43.10483722426597</v>
       </c>
       <c r="D8" t="n">
-        <v>1.993821452969128</v>
+        <v>1.992620745517174</v>
       </c>
       <c r="E8" t="n">
-        <v>9.636841722807821</v>
+        <v>9.635095624708146</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495219241646087</v>
+        <v>0.7495066191338959</v>
       </c>
       <c r="G8" t="n">
-        <v>30.83445826630696</v>
+        <v>30.81968767571359</v>
       </c>
       <c r="H8" t="n">
-        <v>34.478008511572</v>
+        <v>34.47730448015921</v>
       </c>
       <c r="I8" t="n">
-        <v>5.639392722983119</v>
+        <v>5.638979287049218</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684512026028806</v>
+        <v>4.684416369586851</v>
       </c>
       <c r="K8" t="n">
-        <v>11.98344337316755</v>
+        <v>12.0023891981319</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70643231218283</v>
+        <v>44.70520824747633</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81242086129562</v>
+        <v>99.81243466987419</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.03002515817289</v>
+        <v>86.02509005008052</v>
       </c>
       <c r="C9" t="n">
-        <v>42.01136088689217</v>
+        <v>42.00758148093096</v>
       </c>
       <c r="D9" t="n">
-        <v>1.904016844834136</v>
+        <v>1.903490093768194</v>
       </c>
       <c r="E9" t="n">
-        <v>9.987462192078224</v>
+        <v>9.988734526986162</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508891984497974</v>
+        <v>0.7508738436549605</v>
       </c>
       <c r="G9" t="n">
-        <v>29.44562957377942</v>
+        <v>29.44111182006405</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54090312869068</v>
+        <v>34.54019680812818</v>
       </c>
       <c r="I9" t="n">
-        <v>4.708066730029399</v>
+        <v>4.707721434635458</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693057490311235</v>
+        <v>4.692961522843504</v>
       </c>
       <c r="K9" t="n">
-        <v>13.96997484182711</v>
+        <v>13.97490994991947</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86201447342007</v>
+        <v>43.86087025562041</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84335020213935</v>
+        <v>99.84336168647086</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.80326021800479</v>
+        <v>83.87446676831993</v>
       </c>
       <c r="C10" t="n">
-        <v>40.51513102592202</v>
+        <v>40.5874372019677</v>
       </c>
       <c r="D10" t="n">
-        <v>1.804266113237488</v>
+        <v>1.807266950580703</v>
       </c>
       <c r="E10" t="n">
-        <v>10.1191429730676</v>
+        <v>10.13866619589808</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520628341768525</v>
+        <v>0.7520463713351775</v>
       </c>
       <c r="G10" t="n">
-        <v>27.90298403454614</v>
+        <v>27.95283703075174</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59489037213521</v>
+        <v>34.59413308141816</v>
       </c>
       <c r="I10" t="n">
-        <v>3.929521177236181</v>
+        <v>3.929227317491208</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700392713605329</v>
+        <v>4.70028982084486</v>
       </c>
       <c r="K10" t="n">
-        <v>16.1967397819952</v>
+        <v>16.12553323168006</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15734956069308</v>
+        <v>43.15625952650123</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86922036861029</v>
+        <v>99.869229960149</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.46874481776524</v>
+        <v>81.59660115813668</v>
       </c>
       <c r="C11" t="n">
-        <v>38.78970738496022</v>
+        <v>38.91867695470066</v>
       </c>
       <c r="D11" t="n">
-        <v>1.700783657895448</v>
+        <v>1.706370524611825</v>
       </c>
       <c r="E11" t="n">
-        <v>10.08526545261545</v>
+        <v>10.11909987481857</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530718140445603</v>
+        <v>0.7530536705949374</v>
       </c>
       <c r="G11" t="n">
-        <v>26.30262736981698</v>
+        <v>26.39228099270371</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64130344604977</v>
+        <v>34.64046884736712</v>
       </c>
       <c r="I11" t="n">
-        <v>3.278994239564528</v>
+        <v>3.278741806822155</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706698837778503</v>
+        <v>4.70658544121836</v>
       </c>
       <c r="K11" t="n">
-        <v>18.53125518223474</v>
+        <v>18.40339884186332</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56988406677069</v>
+        <v>42.56877900017236</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89084663396567</v>
+        <v>99.89085479673635</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.94067635424547</v>
+        <v>79.09778236887753</v>
       </c>
       <c r="C12" t="n">
-        <v>36.76909569745884</v>
+        <v>36.92736707997295</v>
       </c>
       <c r="D12" t="n">
-        <v>1.589731414644786</v>
+        <v>1.59664010199104</v>
       </c>
       <c r="E12" t="n">
-        <v>9.882692509767018</v>
+        <v>9.92428347288187</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539417255785942</v>
+        <v>0.7539217644677656</v>
       </c>
       <c r="G12" t="n">
-        <v>24.58520389902773</v>
+        <v>24.69509031489668</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68131937661533</v>
+        <v>34.68040116551722</v>
       </c>
       <c r="I12" t="n">
-        <v>2.73565164374579</v>
+        <v>2.735434521199414</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712135784866215</v>
+        <v>4.712011027923536</v>
       </c>
       <c r="K12" t="n">
-        <v>21.05932364575454</v>
+        <v>20.90221763112249</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08049748346538</v>
+        <v>42.07933912760394</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90891682667875</v>
+        <v>99.90892383869938</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.46662964476084</v>
+        <v>76.60479190306236</v>
       </c>
       <c r="C13" t="n">
-        <v>34.71747445672042</v>
+        <v>34.8568666496999</v>
       </c>
       <c r="D13" t="n">
-        <v>1.482126979367656</v>
+        <v>1.488208839020172</v>
       </c>
       <c r="E13" t="n">
-        <v>9.594090507759381</v>
+        <v>9.630602719164816</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546917163639661</v>
+        <v>0.7546703219519022</v>
       </c>
       <c r="G13" t="n">
-        <v>22.92110079497032</v>
+        <v>23.01799362373583</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71581895274244</v>
+        <v>34.71483480978751</v>
       </c>
       <c r="I13" t="n">
-        <v>2.281977466282301</v>
+        <v>2.28179207720274</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71682322727479</v>
+        <v>4.71668951219939</v>
       </c>
       <c r="K13" t="n">
-        <v>23.53337035523916</v>
+        <v>23.39520809693764</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67316486460303</v>
+        <v>41.67194096110694</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9240096765626</v>
+        <v>99.92401570774447</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.3135189777512</v>
+        <v>83.46305878806204</v>
       </c>
       <c r="C14" t="n">
-        <v>38.9969841995312</v>
+        <v>39.0944145764714</v>
       </c>
       <c r="D14" t="n">
-        <v>1.483852660800638</v>
+        <v>1.489985053616673</v>
       </c>
       <c r="E14" t="n">
-        <v>11.97273012947667</v>
+        <v>11.99511291611831</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555704248016938</v>
+        <v>0.7555710399198717</v>
       </c>
       <c r="G14" t="n">
-        <v>24.83023625168787</v>
+        <v>24.9004057317018</v>
       </c>
       <c r="H14" t="n">
-        <v>36.63868732601536</v>
+        <v>36.61120739124542</v>
       </c>
       <c r="I14" t="n">
-        <v>2.91012702995837</v>
+        <v>2.988457655960793</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722315155010588</v>
+        <v>4.722318999499199</v>
       </c>
       <c r="K14" t="n">
-        <v>16.6864810222488</v>
+        <v>16.53694121193793</v>
       </c>
       <c r="L14" t="n">
-        <v>44.21964335724921</v>
+        <v>44.26914770796596</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90310857902921</v>
+        <v>99.90050349637529</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.48912579554109</v>
+        <v>82.60851613385452</v>
       </c>
       <c r="C15" t="n">
-        <v>38.62218059427319</v>
+        <v>38.70159565047698</v>
       </c>
       <c r="D15" t="n">
-        <v>1.45332650751909</v>
+        <v>1.458280244418241</v>
       </c>
       <c r="E15" t="n">
-        <v>12.13100519812236</v>
+        <v>12.15535467717993</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563115874069184</v>
+        <v>0.7563310716559423</v>
       </c>
       <c r="G15" t="n">
-        <v>24.31942300327069</v>
+        <v>24.37055973709207</v>
       </c>
       <c r="H15" t="n">
-        <v>36.67462735762484</v>
+        <v>36.64803474174334</v>
       </c>
       <c r="I15" t="n">
-        <v>2.427484720303933</v>
+        <v>2.49288646391535</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726947421293242</v>
+        <v>4.727069197849641</v>
       </c>
       <c r="K15" t="n">
-        <v>17.51087420445894</v>
+        <v>17.39148386614548</v>
       </c>
       <c r="L15" t="n">
-        <v>43.78610833932458</v>
+        <v>43.82390777071195</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91916313805672</v>
+        <v>99.91698728733441</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.02994597117323</v>
+        <v>80.04864826493913</v>
       </c>
       <c r="C16" t="n">
-        <v>36.53803712754899</v>
+        <v>36.52689209253015</v>
       </c>
       <c r="D16" t="n">
-        <v>1.360181324874596</v>
+        <v>1.361179902477856</v>
       </c>
       <c r="E16" t="n">
-        <v>11.69095162997426</v>
+        <v>11.69251812253732</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569493636070581</v>
+        <v>0.7569859095327111</v>
       </c>
       <c r="G16" t="n">
-        <v>22.76076630381005</v>
+        <v>22.74783345192988</v>
       </c>
       <c r="H16" t="n">
-        <v>36.70555403502493</v>
+        <v>36.67976492202735</v>
       </c>
       <c r="I16" t="n">
-        <v>2.024609791338221</v>
+        <v>2.079204021854582</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730933522544116</v>
+        <v>4.731161934579446</v>
       </c>
       <c r="K16" t="n">
-        <v>19.97005402882677</v>
+        <v>19.95135173506087</v>
       </c>
       <c r="L16" t="n">
-        <v>43.42447871250469</v>
+        <v>43.45250932618912</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93256986888045</v>
+        <v>99.93075315378013</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.74405782783408</v>
+        <v>81.70731101126411</v>
       </c>
       <c r="C17" t="n">
-        <v>37.79482333023111</v>
+        <v>37.73214956471493</v>
       </c>
       <c r="D17" t="n">
-        <v>1.361291390590752</v>
+        <v>1.362336753109878</v>
       </c>
       <c r="E17" t="n">
-        <v>12.48076200503263</v>
+        <v>12.46337545488042</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575671220794323</v>
+        <v>0.7576292628663014</v>
       </c>
       <c r="G17" t="n">
-        <v>23.22604777184351</v>
+        <v>23.18087619961868</v>
       </c>
       <c r="H17" t="n">
-        <v>37.18221606717614</v>
+        <v>37.12464825279935</v>
       </c>
       <c r="I17" t="n">
-        <v>2.001378958115157</v>
+        <v>2.0832621950751</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734794512996455</v>
+        <v>4.735182892914385</v>
       </c>
       <c r="K17" t="n">
-        <v>18.25594217216593</v>
+        <v>18.29268898873589</v>
       </c>
       <c r="L17" t="n">
-        <v>43.88257626651345</v>
+        <v>43.90577834125713</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93334176891048</v>
+        <v>99.93061689470795</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.43303354951414</v>
+        <v>79.21644037100319</v>
       </c>
       <c r="C18" t="n">
-        <v>35.79261331096459</v>
+        <v>35.56268900175257</v>
       </c>
       <c r="D18" t="n">
-        <v>1.277315154310874</v>
+        <v>1.271568336070855</v>
       </c>
       <c r="E18" t="n">
-        <v>11.98900455344767</v>
+        <v>11.9225315750556</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580977020609805</v>
+        <v>0.7581831231473516</v>
       </c>
       <c r="G18" t="n">
-        <v>21.79326410111916</v>
+        <v>21.63640385574788</v>
       </c>
       <c r="H18" t="n">
-        <v>37.20825750817834</v>
+        <v>37.15178800191278</v>
       </c>
       <c r="I18" t="n">
-        <v>1.668983892515967</v>
+        <v>1.737320959397767</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738110637881131</v>
+        <v>4.738644519670949</v>
       </c>
       <c r="K18" t="n">
-        <v>20.56696645048588</v>
+        <v>20.78355962899681</v>
       </c>
       <c r="L18" t="n">
-        <v>43.58482637860189</v>
+        <v>43.59588297494299</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94440614005235</v>
+        <v>99.94213160569237</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.55383921045292</v>
+        <v>78.19794585018643</v>
       </c>
       <c r="C19" t="n">
-        <v>35.1702904902825</v>
+        <v>34.81148694689906</v>
       </c>
       <c r="D19" t="n">
-        <v>1.246019106074394</v>
+        <v>1.235148087682632</v>
       </c>
       <c r="E19" t="n">
-        <v>11.92719699806505</v>
+        <v>11.82249011887676</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758545378043615</v>
+        <v>0.7586513156217952</v>
       </c>
       <c r="G19" t="n">
-        <v>21.25929795953138</v>
+        <v>21.01669417888601</v>
       </c>
       <c r="H19" t="n">
-        <v>37.23022993098981</v>
+        <v>37.17472993641855</v>
       </c>
       <c r="I19" t="n">
-        <v>1.391641224976075</v>
+        <v>1.448661490064452</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740908612772596</v>
+        <v>4.741570722636221</v>
       </c>
       <c r="K19" t="n">
-        <v>21.44616078954706</v>
+        <v>21.80205414981357</v>
       </c>
       <c r="L19" t="n">
-        <v>43.33718805648945</v>
+        <v>43.33819998774854</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95363933631901</v>
+        <v>99.95174108446118</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.08397797106291</v>
+        <v>75.48951010118738</v>
       </c>
       <c r="C20" t="n">
-        <v>32.91448170579331</v>
+        <v>32.32575093679932</v>
       </c>
       <c r="D20" t="n">
-        <v>1.157229504663517</v>
+        <v>1.137577384199884</v>
       </c>
       <c r="E20" t="n">
-        <v>11.27066316183502</v>
+        <v>11.08988108181156</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589309752263455</v>
+        <v>0.7590559395766097</v>
       </c>
       <c r="G20" t="n">
-        <v>19.74438973468979</v>
+        <v>19.35647735438927</v>
       </c>
       <c r="H20" t="n">
-        <v>37.24915545896656</v>
+        <v>37.19455694513296</v>
       </c>
       <c r="I20" t="n">
-        <v>1.160290540517001</v>
+        <v>1.207861773723274</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743318595164661</v>
+        <v>4.744099622353811</v>
       </c>
       <c r="K20" t="n">
-        <v>23.91602202893711</v>
+        <v>24.51048989881263</v>
       </c>
       <c r="L20" t="n">
-        <v>43.13083956457581</v>
+        <v>43.12351856744181</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96134329930622</v>
+        <v>99.95975940305377</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.986539693306</v>
+        <v>81.53916708195777</v>
       </c>
       <c r="C21" t="n">
-        <v>36.59990558696934</v>
+        <v>36.0606177749852</v>
       </c>
       <c r="D21" t="n">
-        <v>1.15800253206955</v>
+        <v>1.138400900902547</v>
       </c>
       <c r="E21" t="n">
-        <v>13.25068057596889</v>
+        <v>13.10563781320896</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594379398697229</v>
+        <v>0.7596054364751762</v>
       </c>
       <c r="G21" t="n">
-        <v>21.45623321580415</v>
+        <v>21.0830786801587</v>
       </c>
       <c r="H21" t="n">
-        <v>38.97269209479788</v>
+        <v>38.93407163986563</v>
       </c>
       <c r="I21" t="n">
-        <v>1.643006210610019</v>
+        <v>1.770838633376915</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74648712418577</v>
+        <v>4.747533977969852</v>
       </c>
       <c r="K21" t="n">
-        <v>18.01346030669401</v>
+        <v>18.46083291804224</v>
       </c>
       <c r="L21" t="n">
-        <v>45.33190379240936</v>
+        <v>45.41956405321881</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94526968607269</v>
+        <v>99.94101474624622</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_91_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_91_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.00948193861696</v>
+        <v>45.34277749045786</v>
       </c>
       <c r="M2" t="n">
-        <v>100.9350178684576</v>
+        <v>99.0479024205971</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.07379916237775</v>
+        <v>87.99252026994317</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95119632085406</v>
+        <v>45.92320683015983</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228832750091295</v>
+        <v>2.228645497595961</v>
       </c>
       <c r="E3" t="n">
-        <v>5.721741065249128</v>
+        <v>5.701272491519486</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429442500304315</v>
+        <v>0.742881832531987</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9804532953767</v>
+        <v>33.97159523552081</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17543550139985</v>
+        <v>34.1725642964714</v>
       </c>
       <c r="I3" t="n">
-        <v>6.580990737540162</v>
+        <v>6.532549462978604</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643401562690197</v>
+        <v>4.643011453324918</v>
       </c>
       <c r="K3" t="n">
-        <v>11.92620083762225</v>
+        <v>12.00747973005684</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88638984663584</v>
+        <v>48.83481945785484</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637870051121</v>
+        <v>106.7655060180715</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.19150791528384</v>
+        <v>87.0724615235528</v>
       </c>
       <c r="C4" t="n">
-        <v>42.70570660497867</v>
+        <v>42.63163484730268</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186519035570798</v>
+        <v>2.184261699486961</v>
       </c>
       <c r="E4" t="n">
-        <v>6.529062405696673</v>
+        <v>6.496924126147514</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445051760198567</v>
+        <v>0.7444332373618968</v>
       </c>
       <c r="G4" t="n">
-        <v>33.3353446841726</v>
+        <v>33.29504599249384</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24723809691341</v>
+        <v>34.24392891864725</v>
       </c>
       <c r="I4" t="n">
-        <v>5.495681166786398</v>
+        <v>5.455159815903482</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653157350124105</v>
+        <v>4.652707733511854</v>
       </c>
       <c r="K4" t="n">
-        <v>12.80849208471616</v>
+        <v>12.92753847644721</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30299601204018</v>
+        <v>44.25936696894515</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81719470173502</v>
+        <v>99.81854029269505</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.0601360792049</v>
+        <v>85.81394057009558</v>
       </c>
       <c r="C5" t="n">
-        <v>42.42734851632353</v>
+        <v>42.21980518757515</v>
       </c>
       <c r="D5" t="n">
-        <v>2.131472086819653</v>
+        <v>2.122521705215273</v>
       </c>
       <c r="E5" t="n">
-        <v>7.129334699671099</v>
+        <v>7.072284448168165</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458281636355483</v>
+        <v>0.7457500999287514</v>
       </c>
       <c r="G5" t="n">
-        <v>32.49610707380695</v>
+        <v>32.35393351071798</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30809552723522</v>
+        <v>34.30450459672256</v>
       </c>
       <c r="I5" t="n">
-        <v>4.58787250531424</v>
+        <v>4.55400808478817</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661426022722178</v>
+        <v>4.660938124554696</v>
       </c>
       <c r="K5" t="n">
-        <v>13.9398639207951</v>
+        <v>14.18605942990443</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48012975269285</v>
+        <v>43.442603165412</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84734218981149</v>
+        <v>99.84846778289156</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.69928954160409</v>
+        <v>84.43809408958079</v>
       </c>
       <c r="C6" t="n">
-        <v>41.77910000095942</v>
+        <v>41.55114440640262</v>
       </c>
       <c r="D6" t="n">
-        <v>2.065115217254673</v>
+        <v>2.055315597936872</v>
       </c>
       <c r="E6" t="n">
-        <v>7.545549366286759</v>
+        <v>7.481802485743533</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469520484285483</v>
+        <v>0.7468690154989004</v>
       </c>
       <c r="G6" t="n">
-        <v>31.48444008937852</v>
+        <v>31.32950020525078</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35979422771322</v>
+        <v>34.35597471294941</v>
       </c>
       <c r="I6" t="n">
-        <v>3.828988289863938</v>
+        <v>3.800700725333154</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668450302678428</v>
+        <v>4.667931346868127</v>
       </c>
       <c r="K6" t="n">
-        <v>15.30071045839592</v>
+        <v>15.56190591041922</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79274863771926</v>
+        <v>42.76044945860073</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8725590970746</v>
+        <v>99.87349977542257</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.12152468930702</v>
+        <v>82.87506291687291</v>
       </c>
       <c r="C7" t="n">
-        <v>40.79609579819922</v>
+        <v>40.57833123246294</v>
       </c>
       <c r="D7" t="n">
-        <v>1.988373510114499</v>
+        <v>1.97922700815233</v>
       </c>
       <c r="E7" t="n">
-        <v>7.797634638025388</v>
+        <v>7.733371644053578</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479090592096175</v>
+        <v>0.7478216698327982</v>
       </c>
       <c r="G7" t="n">
-        <v>30.31444741263893</v>
+        <v>30.16966981634849</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40381672364241</v>
+        <v>34.39979681230871</v>
       </c>
       <c r="I7" t="n">
-        <v>3.194911725616077</v>
+        <v>3.171290529722021</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67443162006011</v>
+        <v>4.673885436454989</v>
       </c>
       <c r="K7" t="n">
-        <v>16.87847531069296</v>
+        <v>17.12493708312708</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21906810527827</v>
+        <v>42.19115666426184</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89363921417045</v>
+        <v>99.89442497985186</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.99761080186809</v>
+        <v>87.93599176007733</v>
       </c>
       <c r="C8" t="n">
-        <v>43.10483722426597</v>
+        <v>42.97669277483458</v>
       </c>
       <c r="D8" t="n">
-        <v>1.992620745517174</v>
+        <v>1.983509513421217</v>
       </c>
       <c r="E8" t="n">
-        <v>9.635095624708146</v>
+        <v>9.635006914681881</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495066191338959</v>
+        <v>0.7494397511484108</v>
       </c>
       <c r="G8" t="n">
-        <v>30.81968767571359</v>
+        <v>30.70172639033097</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47730448015921</v>
+        <v>34.47422855282689</v>
       </c>
       <c r="I8" t="n">
-        <v>5.638979287049218</v>
+        <v>5.708082192990393</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684416369586851</v>
+        <v>4.683998444677568</v>
       </c>
       <c r="K8" t="n">
-        <v>12.0023891981319</v>
+        <v>12.06400823992269</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70520824747633</v>
+        <v>44.76944038084018</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81243466987419</v>
+        <v>99.81014139559744</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.02509005008052</v>
+        <v>85.93765096807638</v>
       </c>
       <c r="C9" t="n">
-        <v>42.00758148093096</v>
+        <v>41.86413097105245</v>
       </c>
       <c r="D9" t="n">
-        <v>1.903490093768194</v>
+        <v>1.893342462042102</v>
       </c>
       <c r="E9" t="n">
-        <v>9.988734526986162</v>
+        <v>9.991270106839366</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508738436549605</v>
+        <v>0.7508250484608263</v>
       </c>
       <c r="G9" t="n">
-        <v>29.44111182006405</v>
+        <v>29.30607684989106</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54019680812818</v>
+        <v>34.53795222919801</v>
       </c>
       <c r="I9" t="n">
-        <v>4.707721434635458</v>
+        <v>4.765527718764863</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692961522843504</v>
+        <v>4.692656552880165</v>
       </c>
       <c r="K9" t="n">
-        <v>13.97490994991947</v>
+        <v>14.06234903192361</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86087025562041</v>
+        <v>43.91496215832979</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84336168647086</v>
+        <v>99.84144216130584</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.87446676831993</v>
+        <v>83.6575095750637</v>
       </c>
       <c r="C10" t="n">
-        <v>40.5874372019677</v>
+        <v>40.32325192404912</v>
       </c>
       <c r="D10" t="n">
-        <v>1.807266950580703</v>
+        <v>1.791369655638932</v>
       </c>
       <c r="E10" t="n">
-        <v>10.13866619589808</v>
+        <v>10.11608195353499</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520463713351775</v>
+        <v>0.7520150021833962</v>
       </c>
       <c r="G10" t="n">
-        <v>27.95283703075174</v>
+        <v>27.72769208275963</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59413308141816</v>
+        <v>34.59269010043622</v>
       </c>
       <c r="I10" t="n">
-        <v>3.929227317491208</v>
+        <v>3.977567016864307</v>
       </c>
       <c r="J10" t="n">
-        <v>4.70028982084486</v>
+        <v>4.700093763646227</v>
       </c>
       <c r="K10" t="n">
-        <v>16.12553323168006</v>
+        <v>16.34249042493629</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15625952650123</v>
+        <v>43.20188188104889</v>
       </c>
       <c r="M10" t="n">
-        <v>99.869229960149</v>
+        <v>99.86762423003429</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.59660115813668</v>
+        <v>81.31633212828557</v>
       </c>
       <c r="C11" t="n">
-        <v>38.91867695470066</v>
+        <v>38.5984211107922</v>
       </c>
       <c r="D11" t="n">
-        <v>1.706370524611825</v>
+        <v>1.687849989884211</v>
       </c>
       <c r="E11" t="n">
-        <v>10.11909987481857</v>
+        <v>10.08468534003527</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530536705949374</v>
+        <v>0.7530381873234339</v>
       </c>
       <c r="G11" t="n">
-        <v>26.39228099270371</v>
+        <v>26.12536427312989</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64046884736712</v>
+        <v>34.63975661687795</v>
       </c>
       <c r="I11" t="n">
-        <v>3.278741806822155</v>
+        <v>3.319149050263354</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70658544121836</v>
+        <v>4.706488670771463</v>
       </c>
       <c r="K11" t="n">
-        <v>18.40339884186332</v>
+        <v>18.68366787171441</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56877900017236</v>
+        <v>42.60742304480271</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89085479673635</v>
+        <v>99.88951202730932</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.09778236887753</v>
+        <v>78.94471664701953</v>
       </c>
       <c r="C12" t="n">
-        <v>36.92736707997295</v>
+        <v>36.74031523275444</v>
       </c>
       <c r="D12" t="n">
-        <v>1.59664010199104</v>
+        <v>1.584075922895337</v>
       </c>
       <c r="E12" t="n">
-        <v>9.92428347288187</v>
+        <v>9.926180655807503</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539217644677656</v>
+        <v>0.7539186798787088</v>
       </c>
       <c r="G12" t="n">
-        <v>24.69509031489668</v>
+        <v>24.51909871728242</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68040116551722</v>
+        <v>34.6802592744206</v>
       </c>
       <c r="I12" t="n">
-        <v>2.735434521199414</v>
+        <v>2.769191647493034</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712011027923536</v>
+        <v>4.71199174924193</v>
       </c>
       <c r="K12" t="n">
-        <v>20.90221763112249</v>
+        <v>21.05528335298046</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07933912760394</v>
+        <v>42.11220282953555</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90892383869938</v>
+        <v>99.90780141527046</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.60479190306236</v>
+        <v>76.59798752462616</v>
       </c>
       <c r="C13" t="n">
-        <v>34.8568666496999</v>
+        <v>34.82115480451128</v>
       </c>
       <c r="D13" t="n">
-        <v>1.488208839020172</v>
+        <v>1.482387683392123</v>
       </c>
       <c r="E13" t="n">
-        <v>9.630602719164816</v>
+        <v>9.673975554095062</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546703219519022</v>
+        <v>0.7546765486421186</v>
       </c>
       <c r="G13" t="n">
-        <v>23.01799362373583</v>
+        <v>22.94511861523733</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71483480978751</v>
+        <v>34.71512123753745</v>
       </c>
       <c r="I13" t="n">
-        <v>2.28179207720274</v>
+        <v>2.309979456708825</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71668951219939</v>
+        <v>4.716728429013242</v>
       </c>
       <c r="K13" t="n">
-        <v>23.39520809693764</v>
+        <v>23.40201247537385</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67194096110694</v>
+        <v>41.69991072990673</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92401570774447</v>
+        <v>99.92307800979185</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.46305878806204</v>
+        <v>83.4921479725389</v>
       </c>
       <c r="C14" t="n">
-        <v>39.0944145764714</v>
+        <v>39.20173237669743</v>
       </c>
       <c r="D14" t="n">
-        <v>1.489985053616673</v>
+        <v>1.484062749820337</v>
       </c>
       <c r="E14" t="n">
-        <v>11.99511291611831</v>
+        <v>12.09600999138318</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555710399198717</v>
+        <v>0.7555293170271734</v>
       </c>
       <c r="G14" t="n">
-        <v>24.9004057317018</v>
+        <v>24.9104274389621</v>
       </c>
       <c r="H14" t="n">
-        <v>36.61120739124542</v>
+        <v>36.69372991289584</v>
       </c>
       <c r="I14" t="n">
-        <v>2.988457655960793</v>
+        <v>2.830330331030431</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722318999499199</v>
+        <v>4.722058231419834</v>
       </c>
       <c r="K14" t="n">
-        <v>16.53694121193793</v>
+        <v>16.5078520274611</v>
       </c>
       <c r="L14" t="n">
-        <v>44.26914770796596</v>
+        <v>44.19617773824059</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90050349637529</v>
+        <v>99.90576214239911</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.60851613385452</v>
+        <v>82.83148085496603</v>
       </c>
       <c r="C15" t="n">
-        <v>38.70159565047698</v>
+        <v>38.96690864400626</v>
       </c>
       <c r="D15" t="n">
-        <v>1.458280244418241</v>
+        <v>1.458637568736629</v>
       </c>
       <c r="E15" t="n">
-        <v>12.15535467717993</v>
+        <v>12.29382042484905</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563310716559423</v>
+        <v>0.7562471161620136</v>
       </c>
       <c r="G15" t="n">
-        <v>24.37055973709207</v>
+        <v>24.49522448458002</v>
       </c>
       <c r="H15" t="n">
-        <v>36.64803474174334</v>
+        <v>36.7401573527668</v>
       </c>
       <c r="I15" t="n">
-        <v>2.49288646391535</v>
+        <v>2.360849431858929</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727069197849641</v>
+        <v>4.726544476012585</v>
       </c>
       <c r="K15" t="n">
-        <v>17.39148386614548</v>
+        <v>17.16851914503399</v>
       </c>
       <c r="L15" t="n">
-        <v>43.82390777071195</v>
+        <v>43.78595192398669</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91698728733441</v>
+        <v>99.92137971302692</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.04864826493913</v>
+        <v>80.47788799618989</v>
       </c>
       <c r="C16" t="n">
-        <v>36.52689209253015</v>
+        <v>36.97823248997648</v>
       </c>
       <c r="D16" t="n">
-        <v>1.361179902477856</v>
+        <v>1.369995848516115</v>
       </c>
       <c r="E16" t="n">
-        <v>11.69251812253732</v>
+        <v>11.87488546659135</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569859095327111</v>
+        <v>0.7568638630811014</v>
       </c>
       <c r="G16" t="n">
-        <v>22.74783345192988</v>
+        <v>23.00664439995937</v>
       </c>
       <c r="H16" t="n">
-        <v>36.67976492202735</v>
+        <v>36.77012028203934</v>
       </c>
       <c r="I16" t="n">
-        <v>2.079204021854582</v>
+        <v>1.968978991745747</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731161934579446</v>
+        <v>4.730399144256885</v>
       </c>
       <c r="K16" t="n">
-        <v>19.95135173506087</v>
+        <v>19.52211200381008</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45250932618912</v>
+        <v>43.43407635532849</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93075315378013</v>
+        <v>99.93442084911506</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.70731101126411</v>
+        <v>82.34998269341814</v>
       </c>
       <c r="C17" t="n">
-        <v>37.73214956471493</v>
+        <v>38.34311015213996</v>
       </c>
       <c r="D17" t="n">
-        <v>1.362336753109878</v>
+        <v>1.371070162782741</v>
       </c>
       <c r="E17" t="n">
-        <v>12.46337545488042</v>
+        <v>12.7135227081582</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576292628663014</v>
+        <v>0.7574573755701229</v>
       </c>
       <c r="G17" t="n">
-        <v>23.18087619961868</v>
+        <v>23.53112755167898</v>
       </c>
       <c r="H17" t="n">
-        <v>37.12464825279935</v>
+        <v>37.30539638507665</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0832621950751</v>
+        <v>1.937299912838186</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735182892914385</v>
+        <v>4.734108597313269</v>
       </c>
       <c r="K17" t="n">
-        <v>18.29268898873589</v>
+        <v>17.65001730658184</v>
       </c>
       <c r="L17" t="n">
-        <v>43.90577834125713</v>
+        <v>43.94234647713833</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93061689470795</v>
+        <v>99.93547393586013</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.21644037100319</v>
+        <v>79.97370164519693</v>
       </c>
       <c r="C18" t="n">
-        <v>35.56268900175257</v>
+        <v>36.26596618230744</v>
       </c>
       <c r="D18" t="n">
-        <v>1.271568336070855</v>
+        <v>1.285321047679583</v>
       </c>
       <c r="E18" t="n">
-        <v>11.9225315750556</v>
+        <v>12.18764747258509</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581831231473516</v>
+        <v>0.757967407883183</v>
       </c>
       <c r="G18" t="n">
-        <v>21.63640385574788</v>
+        <v>22.05944986536662</v>
       </c>
       <c r="H18" t="n">
-        <v>37.15178800191278</v>
+        <v>37.3305158944003</v>
       </c>
       <c r="I18" t="n">
-        <v>1.737320959397767</v>
+        <v>1.615503658012256</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738644519670949</v>
+        <v>4.737296299269895</v>
       </c>
       <c r="K18" t="n">
-        <v>20.78355962899681</v>
+        <v>20.02629835480307</v>
       </c>
       <c r="L18" t="n">
-        <v>43.59588297494299</v>
+        <v>43.65392157642174</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94213160569237</v>
+        <v>99.94618611353225</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.19794585018643</v>
+        <v>79.02738521559637</v>
       </c>
       <c r="C19" t="n">
-        <v>34.81148694689906</v>
+        <v>35.56579878920055</v>
       </c>
       <c r="D19" t="n">
-        <v>1.235148087682632</v>
+        <v>1.251690719814521</v>
       </c>
       <c r="E19" t="n">
-        <v>11.82249011887676</v>
+        <v>12.09368886302448</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586513156217952</v>
+        <v>0.758398878083821</v>
       </c>
       <c r="G19" t="n">
-        <v>21.01669417888601</v>
+        <v>21.48226603037498</v>
       </c>
       <c r="H19" t="n">
-        <v>37.17472993641855</v>
+        <v>37.35176615531569</v>
       </c>
       <c r="I19" t="n">
-        <v>1.448661490064452</v>
+        <v>1.349581580959004</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741570722636221</v>
+        <v>4.739992988023883</v>
       </c>
       <c r="K19" t="n">
-        <v>21.80205414981357</v>
+        <v>20.97261478440361</v>
       </c>
       <c r="L19" t="n">
-        <v>43.33819998774854</v>
+        <v>43.41662596727565</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95174108446118</v>
+        <v>99.95503954087982</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.48951010118738</v>
+        <v>76.44982625305047</v>
       </c>
       <c r="C20" t="n">
-        <v>32.32575093679932</v>
+        <v>33.19592741499619</v>
       </c>
       <c r="D20" t="n">
-        <v>1.137577384199884</v>
+        <v>1.159622990145424</v>
       </c>
       <c r="E20" t="n">
-        <v>11.08988108181156</v>
+        <v>11.39167510849558</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590559395766097</v>
+        <v>0.7587709533799981</v>
       </c>
       <c r="G20" t="n">
-        <v>19.35647735438927</v>
+        <v>19.90214449535452</v>
       </c>
       <c r="H20" t="n">
-        <v>37.19455694513296</v>
+        <v>37.37009116851995</v>
       </c>
       <c r="I20" t="n">
-        <v>1.207861773723274</v>
+        <v>1.125203078530013</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744099622353811</v>
+        <v>4.74231845862499</v>
       </c>
       <c r="K20" t="n">
-        <v>24.51048989881263</v>
+        <v>23.55017374694953</v>
       </c>
       <c r="L20" t="n">
-        <v>43.12351856744181</v>
+        <v>43.21641046080541</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95975940305377</v>
+        <v>99.96251162275112</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.53916708195777</v>
+        <v>82.29661488821532</v>
       </c>
       <c r="C21" t="n">
-        <v>36.0606177749852</v>
+        <v>36.89622977667419</v>
       </c>
       <c r="D21" t="n">
-        <v>1.138400900902547</v>
+        <v>1.160338336390786</v>
       </c>
       <c r="E21" t="n">
-        <v>13.10563781320896</v>
+        <v>13.36876428233631</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596054364751762</v>
+        <v>0.759239022707014</v>
       </c>
       <c r="G21" t="n">
-        <v>21.0830786801587</v>
+        <v>21.63064861831348</v>
       </c>
       <c r="H21" t="n">
-        <v>38.93407163986563</v>
+        <v>39.10937088852468</v>
       </c>
       <c r="I21" t="n">
-        <v>1.770838633376915</v>
+        <v>1.523009848024201</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747533977969852</v>
+        <v>4.74524389191884</v>
       </c>
       <c r="K21" t="n">
-        <v>18.46083291804224</v>
+        <v>17.70338511178469</v>
       </c>
       <c r="L21" t="n">
-        <v>45.41956405321881</v>
+        <v>45.34964941435702</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94101474624622</v>
+        <v>99.94926430281591</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_91_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_91_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.34277749045786</v>
+        <v>43.1097321857052</v>
       </c>
       <c r="M2" t="n">
-        <v>99.0479024205971</v>
+        <v>96.6288245604882</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.99252026994317</v>
+        <v>81.53427366461611</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92320683015983</v>
+        <v>43.28982922017168</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228645497595961</v>
+        <v>2.183240159419813</v>
       </c>
       <c r="E3" t="n">
-        <v>5.701272491519486</v>
+        <v>4.156712478017025</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742881832531987</v>
+        <v>0.7376734449214442</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97159523552081</v>
+        <v>32.83957073127301</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1725642964714</v>
+        <v>33.93297846638643</v>
       </c>
       <c r="I3" t="n">
-        <v>6.532549462978604</v>
+        <v>3.073639353839351</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643011453324918</v>
+        <v>4.610459030759026</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00747973005684</v>
+        <v>18.46572633538388</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83481945785484</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7655060180715</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.0724615235528</v>
+        <v>88.61744724124108</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63163484730268</v>
+        <v>42.78922420273101</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184261699486961</v>
+        <v>2.189045003137311</v>
       </c>
       <c r="E4" t="n">
-        <v>6.496924126147514</v>
+        <v>6.480236637378471</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444332373618968</v>
+        <v>0.7396347862076248</v>
       </c>
       <c r="G4" t="n">
-        <v>33.29504599249384</v>
+        <v>33.49407664299101</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24392891864725</v>
+        <v>34.02320016555074</v>
       </c>
       <c r="I4" t="n">
-        <v>5.455159815903482</v>
+        <v>7.068536592178269</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652707733511854</v>
+        <v>4.622717413797655</v>
       </c>
       <c r="K4" t="n">
-        <v>12.92753847644721</v>
+        <v>11.38255275875891</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25936696894515</v>
+        <v>45.59322995653056</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81854029269505</v>
+        <v>99.76500691802049</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.81394057009558</v>
+        <v>87.66510471585322</v>
       </c>
       <c r="C5" t="n">
-        <v>42.21980518757515</v>
+        <v>42.93239173768463</v>
       </c>
       <c r="D5" t="n">
-        <v>2.122521705215273</v>
+        <v>2.144404045251111</v>
       </c>
       <c r="E5" t="n">
-        <v>7.072284448168165</v>
+        <v>7.332030860558371</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457500999287514</v>
+        <v>0.7412951046273799</v>
       </c>
       <c r="G5" t="n">
-        <v>32.35393351071798</v>
+        <v>32.81103556219367</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30450459672256</v>
+        <v>34.09957481285947</v>
       </c>
       <c r="I5" t="n">
-        <v>4.55400808478817</v>
+        <v>5.903669926442088</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660938124554696</v>
+        <v>4.633094403921125</v>
       </c>
       <c r="K5" t="n">
-        <v>14.18605942990443</v>
+        <v>12.33489528414678</v>
       </c>
       <c r="L5" t="n">
-        <v>43.442603165412</v>
+        <v>44.53636473949696</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84846778289156</v>
+        <v>99.80365176132837</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.43809408958079</v>
+        <v>86.51759693511021</v>
       </c>
       <c r="C6" t="n">
-        <v>41.55114440640262</v>
+        <v>42.70121194833783</v>
       </c>
       <c r="D6" t="n">
-        <v>2.055315597936872</v>
+        <v>2.090175600297617</v>
       </c>
       <c r="E6" t="n">
-        <v>7.481802485743533</v>
+        <v>7.968127181172749</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468690154989004</v>
+        <v>0.7427028698143129</v>
       </c>
       <c r="G6" t="n">
-        <v>31.32950020525078</v>
+        <v>31.98129853581943</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35597471294941</v>
+        <v>34.16433201145839</v>
       </c>
       <c r="I6" t="n">
-        <v>3.800700725333154</v>
+        <v>4.929067800208254</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667931346868127</v>
+        <v>4.641892936339456</v>
       </c>
       <c r="K6" t="n">
-        <v>15.56190591041922</v>
+        <v>13.48240306488977</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76044945860073</v>
+        <v>43.65239415548234</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87349977542257</v>
+        <v>99.83600916870995</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.87506291687291</v>
+        <v>85.20180896518552</v>
       </c>
       <c r="C7" t="n">
-        <v>40.57833123246294</v>
+        <v>42.15110896720834</v>
       </c>
       <c r="D7" t="n">
-        <v>1.97922700815233</v>
+        <v>2.028014668652345</v>
       </c>
       <c r="E7" t="n">
-        <v>7.733371644053578</v>
+        <v>8.416853129590601</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478216698327982</v>
+        <v>0.7438983077855346</v>
       </c>
       <c r="G7" t="n">
-        <v>30.16966981634849</v>
+        <v>31.03018834587699</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39979681230871</v>
+        <v>34.21932215813459</v>
       </c>
       <c r="I7" t="n">
-        <v>3.171290529722021</v>
+        <v>4.114167931485873</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673885436454989</v>
+        <v>4.649364423659592</v>
       </c>
       <c r="K7" t="n">
-        <v>17.12493708312708</v>
+        <v>14.79819103481446</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19115666426184</v>
+        <v>42.91378144797139</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89442497985186</v>
+        <v>99.8630814499942</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.93599176007733</v>
+        <v>83.6818419522875</v>
       </c>
       <c r="C8" t="n">
-        <v>42.97669277483458</v>
+        <v>41.27039965171379</v>
       </c>
       <c r="D8" t="n">
-        <v>1.983509513421217</v>
+        <v>1.956364280820781</v>
       </c>
       <c r="E8" t="n">
-        <v>9.635006914681881</v>
+        <v>8.69167674047198</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494397511484108</v>
+        <v>0.7449156225918399</v>
       </c>
       <c r="G8" t="n">
-        <v>30.70172639033097</v>
+        <v>29.93388215843407</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47422855282689</v>
+        <v>34.26611863922464</v>
       </c>
       <c r="I8" t="n">
-        <v>5.708082192990393</v>
+        <v>3.433161869545184</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683998444677568</v>
+        <v>4.655722641199</v>
       </c>
       <c r="K8" t="n">
-        <v>12.06400823992269</v>
+        <v>16.31815804771252</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76944038084018</v>
+        <v>42.29715985803241</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81014139559744</v>
+        <v>99.8857175574587</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.93765096807638</v>
+        <v>81.9986276830944</v>
       </c>
       <c r="C9" t="n">
-        <v>41.86413097105245</v>
+        <v>40.12045257056241</v>
       </c>
       <c r="D9" t="n">
-        <v>1.893342462042102</v>
+        <v>1.877403711674514</v>
       </c>
       <c r="E9" t="n">
-        <v>9.991270106839366</v>
+        <v>8.818256325582238</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508250484608263</v>
+        <v>0.7457829791424216</v>
       </c>
       <c r="G9" t="n">
-        <v>29.30607684989106</v>
+        <v>28.72572455958668</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53795222919801</v>
+        <v>34.3060170405514</v>
       </c>
       <c r="I9" t="n">
-        <v>4.765527718764863</v>
+        <v>2.864299446917006</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692656552880165</v>
+        <v>4.661143619640137</v>
       </c>
       <c r="K9" t="n">
-        <v>14.06234903192361</v>
+        <v>18.00137231690561</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91496215832979</v>
+        <v>41.78280950504462</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84144216130584</v>
+        <v>99.90463439251263</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.6575095750637</v>
+        <v>86.33575074545865</v>
       </c>
       <c r="C10" t="n">
-        <v>40.32325192404912</v>
+        <v>43.14998272705091</v>
       </c>
       <c r="D10" t="n">
-        <v>1.791369655638932</v>
+        <v>1.879486862514479</v>
       </c>
       <c r="E10" t="n">
-        <v>10.11608195353499</v>
+        <v>10.56059691104594</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520150021833962</v>
+        <v>0.7466104934536864</v>
       </c>
       <c r="G10" t="n">
-        <v>27.72769208275963</v>
+        <v>30.01116730580842</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59269010043622</v>
+        <v>35.59765163080578</v>
       </c>
       <c r="I10" t="n">
-        <v>3.977567016864307</v>
+        <v>2.87392195774481</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700093763646227</v>
+        <v>4.666315584085541</v>
       </c>
       <c r="K10" t="n">
-        <v>16.34249042493629</v>
+        <v>13.66424925454134</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20188188104889</v>
+        <v>43.09007679796272</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86762423003429</v>
+        <v>99.90430877955497</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.31633212828557</v>
+        <v>86.12840563032174</v>
       </c>
       <c r="C11" t="n">
-        <v>38.5984211107922</v>
+        <v>43.30718284325469</v>
       </c>
       <c r="D11" t="n">
-        <v>1.687849989884211</v>
+        <v>1.865514281142025</v>
       </c>
       <c r="E11" t="n">
-        <v>10.08468534003527</v>
+        <v>10.91884512237697</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530381873234339</v>
+        <v>0.7473182897294308</v>
       </c>
       <c r="G11" t="n">
-        <v>26.12536427312989</v>
+        <v>29.81656091201096</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63975661687795</v>
+        <v>35.65990288401886</v>
       </c>
       <c r="I11" t="n">
-        <v>3.319149050263354</v>
+        <v>2.449524830234554</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706488670771463</v>
+        <v>4.670739310808944</v>
       </c>
       <c r="K11" t="n">
-        <v>18.68366787171441</v>
+        <v>13.87159436967826</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60742304480271</v>
+        <v>42.73964929210678</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88951202730932</v>
+        <v>99.91842650503973</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.94471664701953</v>
+        <v>84.36646302550999</v>
       </c>
       <c r="C12" t="n">
-        <v>36.74031523275444</v>
+        <v>41.92650778242465</v>
       </c>
       <c r="D12" t="n">
-        <v>1.584075922895337</v>
+        <v>1.789801480047029</v>
       </c>
       <c r="E12" t="n">
-        <v>9.926180655807503</v>
+        <v>10.81618488950147</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539186798787088</v>
+        <v>0.7479214955428608</v>
       </c>
       <c r="G12" t="n">
-        <v>24.51909871728242</v>
+        <v>28.60644133882498</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6802592744206</v>
+        <v>35.68868614949169</v>
       </c>
       <c r="I12" t="n">
-        <v>2.769191647493034</v>
+        <v>2.04291832495908</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71199174924193</v>
+        <v>4.674509347142881</v>
       </c>
       <c r="K12" t="n">
-        <v>21.05528335298046</v>
+        <v>15.63353697449002</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11220282953555</v>
+        <v>42.37191288668993</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90780141527046</v>
+        <v>99.93195764360459</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.59798752462616</v>
+        <v>85.43730433391721</v>
       </c>
       <c r="C13" t="n">
-        <v>34.82115480451128</v>
+        <v>42.8475343582069</v>
       </c>
       <c r="D13" t="n">
-        <v>1.482387683392123</v>
+        <v>1.791113007922346</v>
       </c>
       <c r="E13" t="n">
-        <v>9.673975554095062</v>
+        <v>11.42454491760133</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546765486421186</v>
+        <v>0.7484695562640574</v>
       </c>
       <c r="G13" t="n">
-        <v>22.94511861523733</v>
+        <v>28.91480462434031</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71512123753745</v>
+        <v>36.00223915106915</v>
       </c>
       <c r="I13" t="n">
-        <v>2.309979456708825</v>
+        <v>1.878198350069647</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716728429013242</v>
+        <v>4.67793472665036</v>
       </c>
       <c r="K13" t="n">
-        <v>23.40201247537385</v>
+        <v>14.56269566608281</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69991072990673</v>
+        <v>42.5272092072215</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92307800979185</v>
+        <v>99.93743923151121</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.4921479725389</v>
+        <v>83.63918432620397</v>
       </c>
       <c r="C14" t="n">
-        <v>39.20173237669743</v>
+        <v>41.34167298036891</v>
       </c>
       <c r="D14" t="n">
-        <v>1.484062749820337</v>
+        <v>1.715738888528332</v>
       </c>
       <c r="E14" t="n">
-        <v>12.09600999138318</v>
+        <v>11.20479772016537</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555293170271734</v>
+        <v>0.7489367255611558</v>
       </c>
       <c r="G14" t="n">
-        <v>24.9104274389621</v>
+        <v>27.69800371542519</v>
       </c>
       <c r="H14" t="n">
-        <v>36.69372991289584</v>
+        <v>36.02471052698205</v>
       </c>
       <c r="I14" t="n">
-        <v>2.830330331030431</v>
+        <v>1.566142214784646</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722058231419834</v>
+        <v>4.680854534757224</v>
       </c>
       <c r="K14" t="n">
-        <v>16.5078520274611</v>
+        <v>16.36081567379605</v>
       </c>
       <c r="L14" t="n">
-        <v>44.19617773824059</v>
+        <v>42.24533916944421</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90576214239911</v>
+        <v>99.94782782360917</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.83148085496603</v>
+        <v>82.84784658919581</v>
       </c>
       <c r="C15" t="n">
-        <v>38.96690864400626</v>
+        <v>40.77203388987772</v>
       </c>
       <c r="D15" t="n">
-        <v>1.458637568736629</v>
+        <v>1.682149240326244</v>
       </c>
       <c r="E15" t="n">
-        <v>12.29382042484905</v>
+        <v>11.20656295402508</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562471161620136</v>
+        <v>0.7493365165865019</v>
       </c>
       <c r="G15" t="n">
-        <v>24.49522448458002</v>
+        <v>27.15574975888097</v>
       </c>
       <c r="H15" t="n">
-        <v>36.7401573527668</v>
+        <v>36.04394093119088</v>
       </c>
       <c r="I15" t="n">
-        <v>2.360849431858929</v>
+        <v>1.326753959520498</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726544476012585</v>
+        <v>4.683353228665638</v>
       </c>
       <c r="K15" t="n">
-        <v>17.16851914503399</v>
+        <v>17.1521534108042</v>
       </c>
       <c r="L15" t="n">
-        <v>43.78595192398669</v>
+        <v>42.03161116262201</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92137971302692</v>
+        <v>99.95579846330392</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.47788799618989</v>
+        <v>80.50141067118368</v>
       </c>
       <c r="C16" t="n">
-        <v>36.97823248997648</v>
+        <v>38.6316339350734</v>
       </c>
       <c r="D16" t="n">
-        <v>1.369995848516115</v>
+        <v>1.584307727700439</v>
       </c>
       <c r="E16" t="n">
-        <v>11.87488546659135</v>
+        <v>10.7390936525187</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568638630811014</v>
+        <v>0.7496797267715344</v>
       </c>
       <c r="G16" t="n">
-        <v>23.00664439995937</v>
+        <v>25.57624684130306</v>
       </c>
       <c r="H16" t="n">
-        <v>36.77012028203934</v>
+        <v>36.06044973246037</v>
       </c>
       <c r="I16" t="n">
-        <v>1.968978991745747</v>
+        <v>1.106134698107473</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730399144256885</v>
+        <v>4.685498292322091</v>
       </c>
       <c r="K16" t="n">
-        <v>19.52211200381008</v>
+        <v>19.49858932881633</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43407635532849</v>
+        <v>41.83292245945694</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93442084911506</v>
+        <v>99.96314572334666</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.34998269341814</v>
+        <v>84.75057181479654</v>
       </c>
       <c r="C17" t="n">
-        <v>38.34311015213996</v>
+        <v>41.43971257138728</v>
       </c>
       <c r="D17" t="n">
-        <v>1.371070162782741</v>
+        <v>1.585075343531874</v>
       </c>
       <c r="E17" t="n">
-        <v>12.7135227081582</v>
+        <v>12.24282180506616</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574573755701229</v>
+        <v>0.7500429554655025</v>
       </c>
       <c r="G17" t="n">
-        <v>23.53112755167898</v>
+        <v>26.88185049816571</v>
       </c>
       <c r="H17" t="n">
-        <v>37.30539638507665</v>
+        <v>37.37113310961885</v>
       </c>
       <c r="I17" t="n">
-        <v>1.937299912838186</v>
+        <v>1.231879631289043</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734108597313269</v>
+        <v>4.687768471659392</v>
       </c>
       <c r="K17" t="n">
-        <v>17.65001730658184</v>
+        <v>15.24942818520345</v>
       </c>
       <c r="L17" t="n">
-        <v>43.94234647713833</v>
+        <v>43.26981647473978</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93547393586013</v>
+        <v>99.95895723133053</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.97370164519693</v>
+        <v>86.1636700078583</v>
       </c>
       <c r="C18" t="n">
-        <v>36.26596618230744</v>
+        <v>42.14772198374914</v>
       </c>
       <c r="D18" t="n">
-        <v>1.285321047679583</v>
+        <v>1.586237550502824</v>
       </c>
       <c r="E18" t="n">
-        <v>12.18764747258509</v>
+        <v>12.81605036028104</v>
       </c>
       <c r="F18" t="n">
-        <v>0.757967407883183</v>
+        <v>0.7505929010279709</v>
       </c>
       <c r="G18" t="n">
-        <v>22.05944986536662</v>
+        <v>27.02574467220247</v>
       </c>
       <c r="H18" t="n">
-        <v>37.3305158944003</v>
+        <v>37.39853432533362</v>
       </c>
       <c r="I18" t="n">
-        <v>1.615503658012256</v>
+        <v>1.89530456708554</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737296299269895</v>
+        <v>4.691205631424819</v>
       </c>
       <c r="K18" t="n">
-        <v>20.02629835480307</v>
+        <v>13.83632999214172</v>
       </c>
       <c r="L18" t="n">
-        <v>43.65392157642174</v>
+        <v>43.95281749369523</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94618611353225</v>
+        <v>99.93686946958609</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.02738521559637</v>
+        <v>83.52808975599139</v>
       </c>
       <c r="C19" t="n">
-        <v>35.56579878920055</v>
+        <v>39.80628197757595</v>
       </c>
       <c r="D19" t="n">
-        <v>1.251690719814521</v>
+        <v>1.486260625841166</v>
       </c>
       <c r="E19" t="n">
-        <v>12.09368886302448</v>
+        <v>12.27168678669584</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758398878083821</v>
+        <v>0.75106629446372</v>
       </c>
       <c r="G19" t="n">
-        <v>21.48226603037498</v>
+        <v>25.32237380056885</v>
       </c>
       <c r="H19" t="n">
-        <v>37.35176615531569</v>
+        <v>37.42212130654807</v>
       </c>
       <c r="I19" t="n">
-        <v>1.349581580959004</v>
+        <v>1.580416601475486</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739992988023883</v>
+        <v>4.694164340398251</v>
       </c>
       <c r="K19" t="n">
-        <v>20.97261478440361</v>
+        <v>16.47191024400862</v>
       </c>
       <c r="L19" t="n">
-        <v>43.41662596727565</v>
+        <v>43.66916042932973</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95503954087982</v>
+        <v>99.9473526509143</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.44982625305047</v>
+        <v>80.84182187015421</v>
       </c>
       <c r="C20" t="n">
-        <v>33.19592741499619</v>
+        <v>37.3646219274929</v>
       </c>
       <c r="D20" t="n">
-        <v>1.159622990145424</v>
+        <v>1.384851414649613</v>
       </c>
       <c r="E20" t="n">
-        <v>11.39167510849558</v>
+        <v>11.65399755378884</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587709533799981</v>
+        <v>0.7514743762077519</v>
       </c>
       <c r="G20" t="n">
-        <v>19.90214449535452</v>
+        <v>23.594600146362</v>
       </c>
       <c r="H20" t="n">
-        <v>37.37009116851995</v>
+        <v>37.44245411157569</v>
       </c>
       <c r="I20" t="n">
-        <v>1.125203078530013</v>
+        <v>1.317729416271849</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74231845862499</v>
+        <v>4.69671485129845</v>
       </c>
       <c r="K20" t="n">
-        <v>23.55017374694953</v>
+        <v>19.15817812984579</v>
       </c>
       <c r="L20" t="n">
-        <v>43.21641046080541</v>
+        <v>43.43329948150923</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96251162275112</v>
+        <v>99.95609953884792</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.29661488821532</v>
+        <v>78.02117235855974</v>
       </c>
       <c r="C21" t="n">
-        <v>36.89622977667419</v>
+        <v>34.74729195389594</v>
       </c>
       <c r="D21" t="n">
-        <v>1.160338336390786</v>
+        <v>1.278822580534137</v>
       </c>
       <c r="E21" t="n">
-        <v>13.36876428233631</v>
+        <v>10.9448325855232</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759239022707014</v>
+        <v>0.7518270955223273</v>
       </c>
       <c r="G21" t="n">
-        <v>21.63064861831348</v>
+        <v>21.78811901887399</v>
       </c>
       <c r="H21" t="n">
-        <v>39.10937088852468</v>
+        <v>37.46002846563005</v>
       </c>
       <c r="I21" t="n">
-        <v>1.523009848024201</v>
+        <v>1.09862326546149</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74524389191884</v>
+        <v>4.698919347014546</v>
       </c>
       <c r="K21" t="n">
-        <v>17.70338511178469</v>
+        <v>21.97882764144025</v>
       </c>
       <c r="L21" t="n">
-        <v>45.34964941435702</v>
+        <v>43.23727680976735</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94926430281591</v>
+        <v>99.96339640510354</v>
       </c>
     </row>
   </sheetData>
